--- a/data/mensal_status/manuais_cache.xlsx
+++ b/data/mensal_status/manuais_cache.xlsx
@@ -387,7 +387,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D2"/>
+  <dimension ref="A1:D3"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -415,6 +415,20 @@
         <v>0</v>
       </c>
       <c r="D2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4">
+      <c r="A3" s="2">
+        <v>46149</v>
+      </c>
+      <c r="B3">
+        <v>0</v>
+      </c>
+      <c r="C3">
+        <v>0</v>
+      </c>
+      <c r="D3">
         <v>0</v>
       </c>
     </row>

--- a/data/mensal_status/manuais_cache.xlsx
+++ b/data/mensal_status/manuais_cache.xlsx
@@ -387,7 +387,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D3"/>
+  <dimension ref="A1:D4"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -429,6 +429,20 @@
         <v>0</v>
       </c>
       <c r="D3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4">
+      <c r="A4" s="2">
+        <v>46150</v>
+      </c>
+      <c r="B4">
+        <v>0</v>
+      </c>
+      <c r="C4">
+        <v>0</v>
+      </c>
+      <c r="D4">
         <v>0</v>
       </c>
     </row>

--- a/data/mensal_status/manuais_cache.xlsx
+++ b/data/mensal_status/manuais_cache.xlsx
@@ -387,7 +387,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D4"/>
+  <dimension ref="A1:D5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -443,6 +443,20 @@
         <v>0</v>
       </c>
       <c r="D4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4">
+      <c r="A5" s="2">
+        <v>46151</v>
+      </c>
+      <c r="B5">
+        <v>0</v>
+      </c>
+      <c r="C5">
+        <v>0</v>
+      </c>
+      <c r="D5">
         <v>0</v>
       </c>
     </row>

--- a/data/mensal_status/manuais_cache.xlsx
+++ b/data/mensal_status/manuais_cache.xlsx
@@ -387,7 +387,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D5"/>
+  <dimension ref="A1:D2"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -406,57 +406,15 @@
     </row>
     <row r="2" spans="1:4">
       <c r="A2" s="2">
-        <v>46148</v>
+        <v>46151</v>
       </c>
       <c r="B2">
-        <v>0</v>
+        <v>733</v>
       </c>
       <c r="C2">
-        <v>0</v>
+        <v>733</v>
       </c>
       <c r="D2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4">
-      <c r="A3" s="2">
-        <v>46149</v>
-      </c>
-      <c r="B3">
-        <v>0</v>
-      </c>
-      <c r="C3">
-        <v>0</v>
-      </c>
-      <c r="D3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4">
-      <c r="A4" s="2">
-        <v>46150</v>
-      </c>
-      <c r="B4">
-        <v>0</v>
-      </c>
-      <c r="C4">
-        <v>0</v>
-      </c>
-      <c r="D4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4">
-      <c r="A5" s="2">
-        <v>46151</v>
-      </c>
-      <c r="B5">
-        <v>0</v>
-      </c>
-      <c r="C5">
-        <v>0</v>
-      </c>
-      <c r="D5">
         <v>0</v>
       </c>
     </row>

--- a/data/mensal_status/manuais_cache.xlsx
+++ b/data/mensal_status/manuais_cache.xlsx
@@ -387,7 +387,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D2"/>
+  <dimension ref="A1:D5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -418,6 +418,48 @@
         <v>0</v>
       </c>
     </row>
+    <row r="3" spans="1:4">
+      <c r="A3" s="2">
+        <v>46152</v>
+      </c>
+      <c r="B3">
+        <v>733</v>
+      </c>
+      <c r="C3">
+        <v>0</v>
+      </c>
+      <c r="D3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4">
+      <c r="A4" s="2">
+        <v>46153</v>
+      </c>
+      <c r="B4">
+        <v>748</v>
+      </c>
+      <c r="C4">
+        <v>32</v>
+      </c>
+      <c r="D4">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4">
+      <c r="A5" s="2">
+        <v>46154</v>
+      </c>
+      <c r="B5">
+        <v>774</v>
+      </c>
+      <c r="C5">
+        <v>82</v>
+      </c>
+      <c r="D5">
+        <v>56</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/data/mensal_status/manuais_cache.xlsx
+++ b/data/mensal_status/manuais_cache.xlsx
@@ -387,7 +387,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D5"/>
+  <dimension ref="A1:D6"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -460,6 +460,20 @@
         <v>56</v>
       </c>
     </row>
+    <row r="6" spans="1:4">
+      <c r="A6" s="2">
+        <v>46155</v>
+      </c>
+      <c r="B6">
+        <v>875</v>
+      </c>
+      <c r="C6">
+        <v>299</v>
+      </c>
+      <c r="D6">
+        <v>198</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/data/mensal_status/manuais_cache.xlsx
+++ b/data/mensal_status/manuais_cache.xlsx
@@ -387,7 +387,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D6"/>
+  <dimension ref="A1:D7"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -474,6 +474,20 @@
         <v>198</v>
       </c>
     </row>
+    <row r="7" spans="1:4">
+      <c r="A7" s="2">
+        <v>46156</v>
+      </c>
+      <c r="B7">
+        <v>852</v>
+      </c>
+      <c r="C7">
+        <v>116</v>
+      </c>
+      <c r="D7">
+        <v>139</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/data/mensal_status/manuais_cache.xlsx
+++ b/data/mensal_status/manuais_cache.xlsx
@@ -387,7 +387,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D7"/>
+  <dimension ref="A1:D10"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -488,6 +488,48 @@
         <v>139</v>
       </c>
     </row>
+    <row r="8" spans="1:4">
+      <c r="A8" s="2">
+        <v>46157</v>
+      </c>
+      <c r="B8">
+        <v>854</v>
+      </c>
+      <c r="C8">
+        <v>304</v>
+      </c>
+      <c r="D8">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4">
+      <c r="A9" s="2">
+        <v>46160</v>
+      </c>
+      <c r="B9">
+        <v>706</v>
+      </c>
+      <c r="C9">
+        <v>99</v>
+      </c>
+      <c r="D9">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4">
+      <c r="A10" s="2">
+        <v>46161</v>
+      </c>
+      <c r="B10">
+        <v>752</v>
+      </c>
+      <c r="C10">
+        <v>128</v>
+      </c>
+      <c r="D10">
+        <v>82</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/data/mensal_status/manuais_cache.xlsx
+++ b/data/mensal_status/manuais_cache.xlsx
@@ -387,7 +387,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D10"/>
+  <dimension ref="A1:D11"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -530,6 +530,20 @@
         <v>82</v>
       </c>
     </row>
+    <row r="11" spans="1:4">
+      <c r="A11" s="2">
+        <v>46162</v>
+      </c>
+      <c r="B11">
+        <v>752</v>
+      </c>
+      <c r="C11">
+        <v>0</v>
+      </c>
+      <c r="D11">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/data/mensal_status/manuais_cache.xlsx
+++ b/data/mensal_status/manuais_cache.xlsx
@@ -387,7 +387,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D11"/>
+  <dimension ref="A1:D12"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -544,6 +544,20 @@
         <v>0</v>
       </c>
     </row>
+    <row r="12" spans="1:4">
+      <c r="A12" s="2">
+        <v>46163</v>
+      </c>
+      <c r="B12">
+        <v>761</v>
+      </c>
+      <c r="C12">
+        <v>329</v>
+      </c>
+      <c r="D12">
+        <v>320</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/data/mensal_status/manuais_cache.xlsx
+++ b/data/mensal_status/manuais_cache.xlsx
@@ -387,7 +387,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D12"/>
+  <dimension ref="A1:D13"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -558,6 +558,20 @@
         <v>320</v>
       </c>
     </row>
+    <row r="13" spans="1:4">
+      <c r="A13" s="2">
+        <v>46164</v>
+      </c>
+      <c r="B13">
+        <v>777</v>
+      </c>
+      <c r="C13">
+        <v>136</v>
+      </c>
+      <c r="D13">
+        <v>120</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/data/mensal_status/manuais_cache.xlsx
+++ b/data/mensal_status/manuais_cache.xlsx
@@ -387,7 +387,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D13"/>
+  <dimension ref="A1:D14"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -572,6 +572,20 @@
         <v>120</v>
       </c>
     </row>
+    <row r="14" spans="1:4">
+      <c r="A14" s="2">
+        <v>46167</v>
+      </c>
+      <c r="B14">
+        <v>818</v>
+      </c>
+      <c r="C14">
+        <v>149</v>
+      </c>
+      <c r="D14">
+        <v>108</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/data/mensal_status/manuais_cache.xlsx
+++ b/data/mensal_status/manuais_cache.xlsx
@@ -387,7 +387,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D14"/>
+  <dimension ref="A1:D15"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -586,6 +586,20 @@
         <v>108</v>
       </c>
     </row>
+    <row r="15" spans="1:4">
+      <c r="A15" s="2">
+        <v>46168</v>
+      </c>
+      <c r="B15">
+        <v>822</v>
+      </c>
+      <c r="C15">
+        <v>82</v>
+      </c>
+      <c r="D15">
+        <v>78</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/data/mensal_status/manuais_cache.xlsx
+++ b/data/mensal_status/manuais_cache.xlsx
@@ -387,7 +387,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D15"/>
+  <dimension ref="A1:D16"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -600,6 +600,20 @@
         <v>78</v>
       </c>
     </row>
+    <row r="16" spans="1:4">
+      <c r="A16" s="2">
+        <v>46169</v>
+      </c>
+      <c r="B16">
+        <v>814</v>
+      </c>
+      <c r="C16">
+        <v>101</v>
+      </c>
+      <c r="D16">
+        <v>109</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/data/mensal_status/manuais_cache.xlsx
+++ b/data/mensal_status/manuais_cache.xlsx
@@ -387,7 +387,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D16"/>
+  <dimension ref="A1:D17"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -614,6 +614,20 @@
         <v>109</v>
       </c>
     </row>
+    <row r="17" spans="1:4">
+      <c r="A17" s="2">
+        <v>46170</v>
+      </c>
+      <c r="B17">
+        <v>908</v>
+      </c>
+      <c r="C17">
+        <v>167</v>
+      </c>
+      <c r="D17">
+        <v>73</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/data/mensal_status/manuais_cache.xlsx
+++ b/data/mensal_status/manuais_cache.xlsx
@@ -387,7 +387,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D17"/>
+  <dimension ref="A1:D18"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -628,6 +628,20 @@
         <v>73</v>
       </c>
     </row>
+    <row r="18" spans="1:4">
+      <c r="A18" s="2">
+        <v>46171</v>
+      </c>
+      <c r="B18">
+        <v>610</v>
+      </c>
+      <c r="C18">
+        <v>57</v>
+      </c>
+      <c r="D18">
+        <v>355</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/data/mensal_status/manuais_cache.xlsx
+++ b/data/mensal_status/manuais_cache.xlsx
@@ -387,7 +387,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D18"/>
+  <dimension ref="A1:D19"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -642,6 +642,20 @@
         <v>355</v>
       </c>
     </row>
+    <row r="19" spans="1:4">
+      <c r="A19" s="2">
+        <v>46174</v>
+      </c>
+      <c r="B19">
+        <v>656</v>
+      </c>
+      <c r="C19">
+        <v>138</v>
+      </c>
+      <c r="D19">
+        <v>92</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/data/mensal_status/manuais_cache.xlsx
+++ b/data/mensal_status/manuais_cache.xlsx
@@ -387,7 +387,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D19"/>
+  <dimension ref="A1:D20"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -656,6 +656,20 @@
         <v>92</v>
       </c>
     </row>
+    <row r="20" spans="1:4">
+      <c r="A20" s="2">
+        <v>46175</v>
+      </c>
+      <c r="B20">
+        <v>590</v>
+      </c>
+      <c r="C20">
+        <v>80</v>
+      </c>
+      <c r="D20">
+        <v>146</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/data/mensal_status/manuais_cache.xlsx
+++ b/data/mensal_status/manuais_cache.xlsx
@@ -387,7 +387,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D20"/>
+  <dimension ref="A1:D21"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -670,6 +670,20 @@
         <v>146</v>
       </c>
     </row>
+    <row r="21" spans="1:4">
+      <c r="A21" s="2">
+        <v>46176</v>
+      </c>
+      <c r="B21">
+        <v>590</v>
+      </c>
+      <c r="C21">
+        <v>0</v>
+      </c>
+      <c r="D21">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/data/mensal_status/manuais_cache.xlsx
+++ b/data/mensal_status/manuais_cache.xlsx
@@ -387,7 +387,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D21"/>
+  <dimension ref="A1:D22"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -684,6 +684,20 @@
         <v>0</v>
       </c>
     </row>
+    <row r="22" spans="1:4">
+      <c r="A22" s="2">
+        <v>46181</v>
+      </c>
+      <c r="B22">
+        <v>590</v>
+      </c>
+      <c r="C22">
+        <v>285</v>
+      </c>
+      <c r="D22">
+        <v>285</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/data/mensal_status/manuais_cache.xlsx
+++ b/data/mensal_status/manuais_cache.xlsx
@@ -387,7 +387,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D22"/>
+  <dimension ref="A1:D23"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -698,6 +698,20 @@
         <v>285</v>
       </c>
     </row>
+    <row r="23" spans="1:4">
+      <c r="A23" s="2">
+        <v>46182</v>
+      </c>
+      <c r="B23">
+        <v>700</v>
+      </c>
+      <c r="C23">
+        <v>216</v>
+      </c>
+      <c r="D23">
+        <v>106</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/data/mensal_status/manuais_cache.xlsx
+++ b/data/mensal_status/manuais_cache.xlsx
@@ -387,7 +387,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D23"/>
+  <dimension ref="A1:D24"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -712,6 +712,20 @@
         <v>106</v>
       </c>
     </row>
+    <row r="24" spans="1:4">
+      <c r="A24" s="2">
+        <v>46183</v>
+      </c>
+      <c r="B24">
+        <v>570</v>
+      </c>
+      <c r="C24">
+        <v>60</v>
+      </c>
+      <c r="D24">
+        <v>190</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/data/mensal_status/manuais_cache.xlsx
+++ b/data/mensal_status/manuais_cache.xlsx
@@ -387,7 +387,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D24"/>
+  <dimension ref="A1:D25"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -726,6 +726,20 @@
         <v>190</v>
       </c>
     </row>
+    <row r="25" spans="1:4">
+      <c r="A25" s="2">
+        <v>46184</v>
+      </c>
+      <c r="B25">
+        <v>630</v>
+      </c>
+      <c r="C25">
+        <v>143</v>
+      </c>
+      <c r="D25">
+        <v>83</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/data/mensal_status/manuais_cache.xlsx
+++ b/data/mensal_status/manuais_cache.xlsx
@@ -387,7 +387,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D25"/>
+  <dimension ref="A1:D26"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -740,6 +740,20 @@
         <v>83</v>
       </c>
     </row>
+    <row r="26" spans="1:4">
+      <c r="A26" s="2">
+        <v>46185</v>
+      </c>
+      <c r="B26">
+        <v>634</v>
+      </c>
+      <c r="C26">
+        <v>94</v>
+      </c>
+      <c r="D26">
+        <v>90</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/data/mensal_status/manuais_cache.xlsx
+++ b/data/mensal_status/manuais_cache.xlsx
@@ -387,7 +387,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D26"/>
+  <dimension ref="A1:D27"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -754,6 +754,20 @@
         <v>90</v>
       </c>
     </row>
+    <row r="27" spans="1:4">
+      <c r="A27" s="2">
+        <v>46188</v>
+      </c>
+      <c r="B27">
+        <v>766</v>
+      </c>
+      <c r="C27">
+        <v>168</v>
+      </c>
+      <c r="D27">
+        <v>36</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/data/mensal_status/manuais_cache.xlsx
+++ b/data/mensal_status/manuais_cache.xlsx
@@ -387,7 +387,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D27"/>
+  <dimension ref="A1:D28"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -768,6 +768,20 @@
         <v>36</v>
       </c>
     </row>
+    <row r="28" spans="1:4">
+      <c r="A28" s="2">
+        <v>46190</v>
+      </c>
+      <c r="B28">
+        <v>766</v>
+      </c>
+      <c r="C28">
+        <v>291</v>
+      </c>
+      <c r="D28">
+        <v>291</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/data/mensal_status/manuais_cache.xlsx
+++ b/data/mensal_status/manuais_cache.xlsx
@@ -387,7 +387,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D28"/>
+  <dimension ref="A1:D29"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -782,6 +782,20 @@
         <v>291</v>
       </c>
     </row>
+    <row r="29" spans="1:4">
+      <c r="A29" s="2">
+        <v>46191</v>
+      </c>
+      <c r="B29">
+        <v>766</v>
+      </c>
+      <c r="C29">
+        <v>0</v>
+      </c>
+      <c r="D29">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/data/mensal_status/manuais_cache.xlsx
+++ b/data/mensal_status/manuais_cache.xlsx
@@ -387,7 +387,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D29"/>
+  <dimension ref="A1:D30"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -796,6 +796,20 @@
         <v>0</v>
       </c>
     </row>
+    <row r="30" spans="1:4">
+      <c r="A30" s="2">
+        <v>46197</v>
+      </c>
+      <c r="B30">
+        <v>708</v>
+      </c>
+      <c r="C30">
+        <v>476</v>
+      </c>
+      <c r="D30">
+        <v>534</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/data/mensal_status/manuais_cache.xlsx
+++ b/data/mensal_status/manuais_cache.xlsx
@@ -387,7 +387,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D30"/>
+  <dimension ref="A1:D31"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -810,6 +810,20 @@
         <v>534</v>
       </c>
     </row>
+    <row r="31" spans="1:4">
+      <c r="A31" s="2">
+        <v>46209</v>
+      </c>
+      <c r="B31">
+        <v>587</v>
+      </c>
+      <c r="C31">
+        <v>490</v>
+      </c>
+      <c r="D31">
+        <v>611</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/data/mensal_status/manuais_cache.xlsx
+++ b/data/mensal_status/manuais_cache.xlsx
@@ -387,7 +387,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D31"/>
+  <dimension ref="A1:D32"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -824,6 +824,20 @@
         <v>611</v>
       </c>
     </row>
+    <row r="32" spans="1:4">
+      <c r="A32" s="2">
+        <v>46211</v>
+      </c>
+      <c r="B32">
+        <v>492</v>
+      </c>
+      <c r="C32">
+        <v>235</v>
+      </c>
+      <c r="D32">
+        <v>330</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/data/mensal_status/manuais_cache.xlsx
+++ b/data/mensal_status/manuais_cache.xlsx
@@ -387,7 +387,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D32"/>
+  <dimension ref="A1:D33"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -838,6 +838,20 @@
         <v>330</v>
       </c>
     </row>
+    <row r="33" spans="1:4">
+      <c r="A33" s="2">
+        <v>46216</v>
+      </c>
+      <c r="B33">
+        <v>591</v>
+      </c>
+      <c r="C33">
+        <v>169</v>
+      </c>
+      <c r="D33">
+        <v>70</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/data/mensal_status/manuais_cache.xlsx
+++ b/data/mensal_status/manuais_cache.xlsx
@@ -387,7 +387,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D33"/>
+  <dimension ref="A1:D34"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -852,6 +852,20 @@
         <v>70</v>
       </c>
     </row>
+    <row r="34" spans="1:4">
+      <c r="A34" s="2">
+        <v>46252</v>
+      </c>
+      <c r="B34">
+        <v>609</v>
+      </c>
+      <c r="C34">
+        <v>604</v>
+      </c>
+      <c r="D34">
+        <v>586</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/data/mensal_status/manuais_cache.xlsx
+++ b/data/mensal_status/manuais_cache.xlsx
@@ -387,7 +387,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D34"/>
+  <dimension ref="A1:D35"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -866,6 +866,20 @@
         <v>586</v>
       </c>
     </row>
+    <row r="35" spans="1:4">
+      <c r="A35" s="2">
+        <v>46255</v>
+      </c>
+      <c r="B35">
+        <v>388</v>
+      </c>
+      <c r="C35">
+        <v>65</v>
+      </c>
+      <c r="D35">
+        <v>141</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/data/mensal_status/manuais_cache.xlsx
+++ b/data/mensal_status/manuais_cache.xlsx
@@ -387,7 +387,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D35"/>
+  <dimension ref="A1:D36"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -880,6 +880,20 @@
         <v>141</v>
       </c>
     </row>
+    <row r="36" spans="1:4">
+      <c r="A36" s="2">
+        <v>46261</v>
+      </c>
+      <c r="B36">
+        <v>460</v>
+      </c>
+      <c r="C36">
+        <v>221</v>
+      </c>
+      <c r="D36">
+        <v>230</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/data/mensal_status/manuais_cache.xlsx
+++ b/data/mensal_status/manuais_cache.xlsx
@@ -387,7 +387,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D36"/>
+  <dimension ref="A1:D37"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -894,6 +894,20 @@
         <v>230</v>
       </c>
     </row>
+    <row r="37" spans="1:4">
+      <c r="A37" s="2">
+        <v>46262</v>
+      </c>
+      <c r="B37">
+        <v>479</v>
+      </c>
+      <c r="C37">
+        <v>83</v>
+      </c>
+      <c r="D37">
+        <v>64</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/data/mensal_status/manuais_cache.xlsx
+++ b/data/mensal_status/manuais_cache.xlsx
@@ -387,7 +387,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D37"/>
+  <dimension ref="A1:D38"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -908,6 +908,20 @@
         <v>64</v>
       </c>
     </row>
+    <row r="38" spans="1:4">
+      <c r="A38" s="2">
+        <v>46266</v>
+      </c>
+      <c r="B38">
+        <v>563</v>
+      </c>
+      <c r="C38">
+        <v>168</v>
+      </c>
+      <c r="D38">
+        <v>91</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
